--- a/plantilla_consolidado_2026.xlsx
+++ b/plantilla_consolidado_2026.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Biblioteca</t>
+          <t xml:space="preserve">Departamento de Biblioteca</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Educación Virtual, Medios Educativos y Audiovisuales</t>
+          <t xml:space="preserve">Dpto. de Edu. Virt. Medios Educ y Audiov</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director de Regionalización nivel Sede</t>
+          <t xml:space="preserve">Dirección de Regionalización nivel sede</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Egresados</t>
+          <t xml:space="preserve">Oficina de Egresados</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director de Regionalización nivel Sede</t>
+          <t xml:space="preserve">Dirección de Regionalización nivel sede</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director de Regionalización nivel Sede</t>
+          <t xml:space="preserve">Dirección de Regionalización nivel sede</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Admisiones y Registro</t>
+          <t xml:space="preserve">Dpto. de Admisiones y Registro</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director de Regionalización nivel Sede</t>
+          <t xml:space="preserve">Dirección de Regionalización nivel sede</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director de Regionalización nivel Sede</t>
+          <t xml:space="preserve">Dirección de Regionalización nivel sede</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Postgrado</t>
+          <t xml:space="preserve">Dpto. de Postgrados</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Postgrado</t>
+          <t xml:space="preserve">Dpto. de Postgrados</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Postgrado</t>
+          <t xml:space="preserve">Dpto. de Postgrados</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Calidad Academica</t>
+          <t xml:space="preserve">Dpto. Calidad Académica</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector De Docencia</t>
+          <t xml:space="preserve">Vicerrectoría de Docencia</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Fomento y Apoyo a la Investigación</t>
+          <t xml:space="preserve">Dpto. de Fomento y Apoyo a la Investigación</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Egresados</t>
+          <t xml:space="preserve">Oficina de Egresados</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Egresados</t>
+          <t xml:space="preserve">Oficina de Egresados</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Egresados</t>
+          <t xml:space="preserve">Oficina de Egresados</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director del Museo de Antropología</t>
+          <t xml:space="preserve">Museo de Antropología</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento Extensión y Proyección Social</t>
+          <t xml:space="preserve">Dpto. de Extens. y Proy. Social</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director Consultorio Jurídico y Centro de Conciliación</t>
+          <t xml:space="preserve">Consultorio Jurídico y Centro de Conciliación</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director Consultorio Jurídico y Centro de Conciliación</t>
+          <t xml:space="preserve">Consultorio Jurídico y Centro de Conciliación</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director del Museo de Antropología</t>
+          <t xml:space="preserve">Museo de Antropología</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -14918,7 +14918,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe Departamento de Desarrollo Humano</t>
+          <t xml:space="preserve">Dpto. de Desarrollo Humano</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vicerrector de Bienestar Universitario</t>
+          <t xml:space="preserve">Vice de Bienestar Universitario</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión Financiera</t>
+          <t xml:space="preserve">Dpto. de Gestión Financiera</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión Financiera</t>
+          <t xml:space="preserve">Dpto. de Gestión Financiera</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión Financiera</t>
+          <t xml:space="preserve">Dpto. de Gestión Financiera</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretario General</t>
+          <t xml:space="preserve">Secretaría General</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretario General</t>
+          <t xml:space="preserve">Secretaría General</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretario General</t>
+          <t xml:space="preserve">Secretaría General</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretario General</t>
+          <t xml:space="preserve">Secretaría General</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director de Comunicaciones</t>
+          <t xml:space="preserve">Dirección de Comunicaciones</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Relaciones Interinstitucionales e Internacionales</t>
+          <t xml:space="preserve">Oficina de Rel. Interinst. e Internacionales</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión de Talento Humano</t>
+          <t xml:space="preserve">Dpto. de Gestión de Talento Humano</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión de Talento Humano</t>
+          <t xml:space="preserve">Dpto. de Gestión de Talento Humano</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión de Talento Humano</t>
+          <t xml:space="preserve">Dpto. de Gestión de Talento Humano</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión de Talento Humano</t>
+          <t xml:space="preserve">Dpto. de Gestión de Talento Humano</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Gestión de Talento Humano</t>
+          <t xml:space="preserve">Dpto. de Gestión de Talento Humano</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
@@ -19238,7 +19238,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Infraestructura Física y Servicios Generales</t>
+          <t xml:space="preserve">Dpto. de Inf Física y Servicios Generales</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe del Departamento de Infraestructura Física y Servicios Generales</t>
+          <t xml:space="preserve">Dpto. de Inf Física y Servicios Generales</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Gestión Tecnológica e Información</t>
+          <t xml:space="preserve">Oficina de Gest. Tec. e Información</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jefe de Oficina de Planeación</t>
+          <t xml:space="preserve">Oficina de Planeación</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
